--- a/校园招聘/制造业/半导体与集成电路/技术研发类/自动化工程师/3_需重新出题/6轮_半导体与集成电路_自动化工程师_需要重新出题.xlsx
+++ b/校园招聘/制造业/半导体与集成电路/技术研发类/自动化工程师/3_需重新出题/6轮_半导体与集成电路_自动化工程师_需要重新出题.xlsx
@@ -1,38 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chengxi5\Desktop\8月AI审题\半导体与集成电路制造业\自动化工程师\6轮审核后需要重出的内容\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/risei/Desktop/北森-测评产品经理/AI面试官/专业能力/8月迭代/出题表格/知识审核/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A83EDED-212C-F346-B358-9ECA67F0D80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="5530"/>
+    <workbookView xWindow="4360" yWindow="760" windowWidth="25040" windowHeight="16580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="出题" sheetId="1" r:id="rId1"/>
+    <sheet name="出答案" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>问题</t>
   </si>
   <si>
-    <t>第一层</t>
-  </si>
-  <si>
-    <t>第二层</t>
-  </si>
-  <si>
-    <t>第三层</t>
-  </si>
-  <si>
     <t>技能分类</t>
   </si>
   <si>
@@ -63,15 +56,6 @@
     <t>请简述对准偏差与晶圆上图形重叠精度之间的关系。</t>
   </si>
   <si>
-    <t>对准偏差是光刻设备在执行套刻（Overlay）动作时，实际曝光图形中心相对于前道层参考标记的偏移量；该偏差直接转化为晶圆上多层图形之间的重叠精度劣化，是影响套刻误差（OVL）的关键可控变量。</t>
-  </si>
-  <si>
-    <t>在自动化工程师日常工作中，主要有三种技术方案用于关联对准偏差与重叠精度：一是通过EAP系统实时采集光刻机对准传感器反馈的X/Y/θ偏差值，并映射至设备Recipe中预设的OVL补偿参数项（如ALIGN_OFFSET_X），该方案响应快、闭环强，被主流Fab在量产线广泛采用；二是依赖设备本地PLC周期性读取对准模块状态寄存器（如ASML TWINSCAN的ALG_STAT_REG），结合运动控制器位置锁存信号做偏差趋势比对，适用于无EAP联机的老产线，但存在100ms级延迟；三是基于SECS/GEM协议订阅S6F11事件上报的对准结果数据包，解析其中ALIGN_RESULT字段，需确保EAP已配置对应Event Report List，该方式兼容性强但需校验ACK码S6F12返回状态。综合来看，第一种方案因与EAP调度逻辑深度耦合、支持自动触发Recipe重同步，在当前主流12英寸Fab中为首选。</t>
-  </si>
-  <si>
-    <t>1个异常情况概要：对准偏差持续超限但EAP未触发OVL补偿重载。具体情况：连续5片晶圆ALIGN_OFFSET_X＞±25nm，EAP日志显示S2F41下发成功但设备未更新补偿参数项，检查发现设备侧PLC未置位‘RECIPE_UPDATE_REQ’信号。解决思路：确认PLC中该信号的触发条件（需同时满足ALIGN_COMPLETE=1且OVL_QUALITY_FLAG=OK），用示波器同步抓取该IO与SECS通信周期信号，验证是否因节拍失衡导致信号脉宽不足；复位后手动触发S2F42确认ACK码为S2F43且DATA=0x00。1个复杂问题概要：同一设备不同腔室间对准偏差分布离散。具体问题：Track1与Track2的ALIGN_OFFSET_Y标准差相差3倍，影响跨Track投片良率。解决思路：调取两Track伺服驱动器的CANopen同步误差寄存器（0x6064），比对主从轴位置锁存时刻抖动；检查机械基准面清洁度及上下料手臂重复定位精度（使用激光跟踪仪实测Z向基准点偏移），优先排查夹具气压稳定性与真空吸附响应时间差异。</t>
-  </si>
-  <si>
     <t>半导体工艺与设备匹配</t>
   </si>
   <si>
@@ -93,20 +77,92 @@
     <t>校园招聘/社会招聘通用</t>
   </si>
   <si>
-    <t xml:space="preserve">题干中涉及协议/标准时，必须区分“标准强制要求”和“厂商常见实现”，禁止把可配置实现写成唯一必选做法。
-</t>
+    <t>1. 岗位通用职责：围绕半导体产线及设备自动化需求，完成设备控制、联机集成、故障处理、数据采集和稳定性提升的技术闭环。
+2. 电气控制方向：负责半导体设备或产线电气控制方案、控制柜、PLC/HMI、伺服驱动、传感器与安全回路的设计、调试和维护。
+3. 设备软件与运动控制方向：开发和维护半导体设备控制软件、调试软件、数据采集程序及硬件驱动接口，保障设备动作精度、吞吐量和运行稳定性。
+4. CIM/EAP/MES系统集成方向：负责半导体制造自动化系统的需求分析、设计开发、运行维护和跨系统集成，实现设备数据采集、参数下发、报警上报和生产自动化控制。
+5. 设备联调与现场问题处理方向：参与新设备安装、集成调试、试运行、量产导入和现场异常处理，确保设备满足半导体生产节拍、精度、稳定性和联机要求。
+6. 自动化改善与智能制造方向：根据产线效率、良率、停机率、数据透明度等目标，推动设备自动化、少人化、数据化和系统功能优化。
+7. 机械结构与设备机构方向：理解半导体自动化设备的关键机械结构、传动机构、夹治具、上下料机构和装配基准，支持控制方案设计、联调问题定位和设备稳定性改善。
+8. 半导体工艺与设备匹配方向：理解主要半导体制程、设备Recipe、工艺参数窗口和自动化动作之间的关系，在设备调试、联机、异常处理和数据分析中识别工艺约束并保障量产稳定性。</t>
+  </si>
+  <si>
+    <t>你是一位经验丰富的资深面试官，拥有超过 10 年人才招聘经验。你尤其擅长从知识深度、逻辑思维以及实战能力等多个维度全面评估候选人。
+现在请依据以下要求，为【{{industry}}】行业下的【{{job}}】岗位的候选人精心准备【{{num}}】道视频面试题。
+关于目标行业下岗位的岗位描述：【{{JD}}】
+## 面试题要求
+- 题目类型：必须为简答题。
+- 内容相关性：题目内容要紧密围绕【{{category}}】技能分类下【{{skill}}】技能里的【{{knowledge}}】知识点展开。
+- 行业岗位适用性：题目需与【{{industry}}】行业下的【{{job}}】岗位职责高度适配，贴合该行业实际情况。
+- 招聘场景：题目应契合【{{scene}}】这一特定招聘场景。
+- 题目难度：全部设定为【{{level}}】难度，具体难度定义如下：
+    · 简单：考察应聘者能否识别、回忆出关键概念，是否了解关键概念背后的基本原理。提问需从小而具体的切入点考察对某知识点的概念识别与规则理解，无场景，纯理论考察。如“请简述什么是负载均衡技术中轮询策略”。建议作答时间控制在60秒内。字数控制在10～30字。
+    · 中等：考察应聘者是否知道在一个简单应用场景下用何种方法解决问题，解决机制是什么。提问内容涉及概念与规则的基础应用，场景是这个知识点常见的简单应用场景，禁止涉及穷举、优劣势分析、系统性设计或冲突情况。如“当一个服务有多个实例时，负载均衡器是怎么判断某个实例‘可用’从而把请求转发过去的？”建议作答时间控制在90秒内。字数控制在30～60字。
+    · 困难：考察应聘者是否知道在复杂/业务场景下如何运用知识点进行系统设计或优化来解决问题。提问内容涉及通过多规则整合进行复杂问题解决，需要候选人分析多方面的因素，权衡不同的选择，提出解决方案，并清晰阐述决策的依据和逻辑。场景应是较为复杂的业务场景。如“线上服务在高峰期出现部分用户延迟很高，但监控显示整体 CPU 并不高，你怀疑是负载均衡分配不均导致的。你会如何定位问题，并调整负载均衡策略来改善长尾延迟？” 。建议作答时间控制在120秒内。字数控制在60～90字。对于困难题，复杂场景应改变真实决策变量，而不是堆叠标准名和参数；题干必须让候选人能围绕一个明确工程问题展开判断。
+- 题干长度：一个题目里只能有1个小问，禁止连环提问！使读题时间控制在30秒内，难度越低的题题干应越好理解。
+-易答性：
+1.禁用词：写代码、写出、编写、绘制、计算等一些口头无法表述的内容，确保候选人仅通过口头回答即可完成答题；
+2.不能出现让候选人讲述某一个软件的操作步骤；
+3.提问应该逻辑严谨，简单易懂，提出问题时需要模仿面试官在面试的口吻，不能过于生硬而让候选人不能明白题目的意思；
+4.编程题要给出规定的编程语言。
+- 特别注意：
+题干中涉及协议/标准时，必须区分“标准强制要求”和“厂商常见实现”，禁止把可配置实现写成唯一必选做法
+- 内容限制：
+1.问题中的应用场景/条件不能是虚构的或者故事化的场景。语言上，类似“假设....”的提问是不被允许的。
+2.技术时效性：题干禁止问旧版本/早期版本的技术，涉及的技术场景必须是2022年之后在用的，但不必在题干中标注年份。
+3.问题中不能出现【{{industry}}】行业名称、【{{scene}}】特定招聘场景名称、【{{job}}】职位
+4.对于【通用行业】的知识点提问需要通用化，业务场景需要是各行各业的应聘者都能看懂的。
+5.所有的问题都是知识点面试问题，不能出行为化面试题
+6.尽量不要出现英文，能用中文的用中文表达！
+7.禁止出现事实、知识错误！
+8.禁止出现“请用一句话回答”这类强势粗暴的提问方法，可以说“请简述”“请简单说说”等
+## 输出规范要求
+- 若题目数量超过 1 道，要保证所有题目内容不重复，从不同主题或提问角度进行设计。
+- 严格以规范的 JSON 格式输出结果，不包含任何额外的文本说明。
+## 输出示例
+{{
+    ""questions"": [{{
+        ""question"": ""题目题干""，
+        ""level"": ""难度"",
+        ""time"": 建议答题时间，整数类型
+    }}]
+}}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>重出答案时增加“协议真实性自检清单”：逐条核对SECS/GEM消息编号-用途映射、状态字段语义、标准必选与工程惯例边界；禁止把未证实字段名当标准字段，禁止把命令消息当配置消息；每题提交前增加一次“是否会误导现场调试”反向审阅。另增“口径规范规则”：凡属于实现差异/厂商口径可变的点，必须明确标注为“可配置/常见实践”，不得表述为“标准强制/唯一正确答案”；若无法确认标准强制性，必须降级为风险提示而非确定结论。</t>
+    <t>你是一位经验丰富的资深面试官，拥有超过 10 年人才招聘经验。你尤其擅长从知识深度、逻辑思维以及实战能力等多个维度全面评估候选人。
+现在请依据以下要求，为面试【{{job}}】职位的候选人的视频面试题【{{Q}}】生成符合规则的参考答案。
+## 参考答案要求
+- 内容相关性：题目内容要紧密围绕【{{category}}】技能分类下【{{skill}}】技能里的【{{knowledge}}】知识点展开。
+- 岗位适用性：答案需与【{{{industry}}】行业的【{{job}}】岗位的工作范畴高度适配，仅从该岗位工作内容角度生成。禁止从技术的口径回答问题！！岗位工作内容参考：【{{JD}}】
+- 使用场景：答案应契合【{{scene}}】这一特定使用场景。
+- 内容与格式：每个题目的三层参考答案字数合计限制在300～600字，每个题目考察的都是一个岗位上某个技能的掌握程度，掌握程度分为以下三个层次，因此参考答案也需要分层生成。对第一层给出回答题干所需的基础知识，内容严格对应题干，不要举例，不要超出题干所问的范围！对第二层给出这个应用场景下常见的2～4种技术方案或方法的分析，优劣势分别是什么，哪种最好，方法要在保证时效性的基础上全面！分析要深入！对第三层给出这个知识点或场景下最最常出现的1个异常情况和1个复杂问题，以及每种情况的解决思路，输出时要结构化！小标题结构为：1个异常情况概要，具体情况，解决思路；1个复杂问题概要，具体问题，解决思路。
+重出答案时按三层结构分别约束：第三层必须基于半导体制造真实异常（如传感器漂移、通讯抖动、设备节拍失衡、误报警）给出可落地排障步骤。统一要求答案避免绝对化结论，补充前提条件、监控指标与验证方式；用岗位语言描述可执行动作，减少空泛原则与过时方案。
+参考答案约束：
+1.参考答案的内容必须严格对应岗位口径
+2.禁止出现代码块、符号等书面表达，所有类似内容必须用口语自然语言描述的形式代替
+3.禁止出现公式、计算等
+4.能用中文的用中文表达
+5.涉及的技术方法必须是2023年之后在用的，但相关时间信息不必出现在答案文本中
+特别注意：
+重出答案时增加“协议真实性自检清单”：逐条核对SECS/GEM消息编号-用途映射、状态字段语义、标准必选与工程惯例边界；禁止把未证实字段名当标准字段，禁止把命令消息当配置消息；每题提交前增加一次“是否会误导现场调试”反向审阅。另增“口径规范规则”：凡属于实现差异/厂商口径可变的点，必须明确标注为“可配置/常见实践”，不得表述为“标准强制/唯一正确答案”；若无法确认标准强制性，必须降级为风险提示而非确定结论。
+## 输出示例
+{{
+    ""questions"": [{{
+        ""question"": ""题目题干""，
+        ""answer1"":""参考答案-第一层"",
+        ""answer2"":""参考答案-第二层"",
+        ""answer3"":""参考答案-第三层""
+    }}]
+}}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,6 +177,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -130,7 +194,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -138,14 +202,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -448,11 +530,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -483,62 +565,70 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+    </row>
+    <row r="2" spans="1:11" ht="409.6">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="196" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
+      <c r="K2" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA88EDFC-96D1-DE4C-B7DC-5CDECCAF82EC}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="409.6">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>